--- a/4.APIs/APITestData.xlsx
+++ b/4.APIs/APITestData.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uipath-my.sharepoint.com/personal/victor_corcodel_uipath_com/Documents/Documents/##Projects/#ILTs/Test Suite/Application Testing ILT/7.APIs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UiPath\ABN-ILT\4.APIs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{2A68C250-226A-4453-896D-B16BC668B50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC5939AC-9638-4825-8A2B-EAB9846B4B20}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC521FA-5DB2-4413-9AA1-2D0C7C5A7FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24720" yWindow="2400" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
   <si>
     <t>Amount</t>
   </si>
@@ -363,13 +374,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -389,7 +400,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2000</v>
       </c>
@@ -400,32 +411,306 @@
         <v>1000</v>
       </c>
       <c r="D2">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2000</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>5000</v>
+      </c>
+      <c r="D3">
+        <f>D2+1</f>
         <v>25</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2000</v>
-      </c>
-      <c r="B3">
-        <v>10</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>16</v>
-      </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
       <c r="F3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2000</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>20000</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ref="D4:D16" si="0">D3+1</f>
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2000</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>2000</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2000</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>1000</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2000</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>5000</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2000</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>20000</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2000</v>
+      </c>
+      <c r="B9">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>2000</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2000</v>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>1000</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2000</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>5000</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="E11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2000</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>20000</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2000</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>2000</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2000</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>1000</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2000</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15">
+        <v>5000</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="E15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2000</v>
+      </c>
+      <c r="B16">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>20000</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="b">
         <v>1</v>
       </c>
     </row>

--- a/4.APIs/APITestData.xlsx
+++ b/4.APIs/APITestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UiPath\ABN-ILT\4.APIs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC521FA-5DB2-4413-9AA1-2D0C7C5A7FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6893E33C-B353-4CA0-840F-D57DC084EE38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24720" yWindow="2400" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>Amount</t>
   </si>
@@ -374,7 +374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="38.140625" customWidth="1"/>
@@ -441,279 +441,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2000</v>
-      </c>
-      <c r="B4">
-        <v>10</v>
-      </c>
-      <c r="C4">
-        <v>20000</v>
-      </c>
-      <c r="D4">
-        <f t="shared" ref="D4:D16" si="0">D3+1</f>
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2000</v>
-      </c>
-      <c r="B5">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>2000</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2000</v>
-      </c>
-      <c r="B6">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>1000</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2000</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>5000</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>2000</v>
-      </c>
-      <c r="B8">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>20000</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2000</v>
-      </c>
-      <c r="B9">
-        <v>10</v>
-      </c>
-      <c r="C9">
-        <v>2000</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>2000</v>
-      </c>
-      <c r="B10">
-        <v>10</v>
-      </c>
-      <c r="C10">
-        <v>1000</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>2000</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11">
-        <v>5000</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>2000</v>
-      </c>
-      <c r="B12">
-        <v>10</v>
-      </c>
-      <c r="C12">
-        <v>20000</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>2000</v>
-      </c>
-      <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13">
-        <v>2000</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>2000</v>
-      </c>
-      <c r="B14">
-        <v>10</v>
-      </c>
-      <c r="C14">
-        <v>1000</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>2000</v>
-      </c>
-      <c r="B15">
-        <v>10</v>
-      </c>
-      <c r="C15">
-        <v>5000</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>2000</v>
-      </c>
-      <c r="B16">
-        <v>10</v>
-      </c>
-      <c r="C16">
-        <v>20000</v>
-      </c>
-      <c r="D16">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
